--- a/demo/Fly91_Weekly_AWS_BAU_Report_14-20_Sep_2026.xlsx
+++ b/demo/Fly91_Weekly_AWS_BAU_Report_14-20_Sep_2026.xlsx
@@ -20,10 +20,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cost Analysis'!$A$4:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cost Analysis'!$A$4:$F$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'EC2 Instances'!$A$4:$H$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Load Balancers'!$A$4:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'WAF'!$A$4:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'WAF'!$A$4:$D$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inspector'!$A$15:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'GuardDuty'!$A$13:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'S3 Storage'!$A$4:$C$20</definedName>
@@ -135,8 +135,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="004472C4"/>
-      <sz val="12"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="9">
@@ -240,7 +239,7 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -315,6 +314,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -324,9 +326,7 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -923,7 +923,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>EC2 Average Memory Usage (%)</a:t>
+              <a:t>EC2 Disk Usage (%)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -959,7 +959,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>Avg Memory (%)</v>
+            <v>Disk Usage (%)</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1063,7 +1063,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>EC2 Disk Usage (%)</a:t>
+              <a:t>EC2 Network Usage (MB)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1099,7 +1099,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>Disk Usage (%)</v>
+            <v>Network In (MB)</v>
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -1117,6 +1117,31 @@
           <val>
             <numRef>
               <f>'Dashboard'!$B$124:$B$131</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Network Out (MB)</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$124:$A$131</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$C$124:$C$131</f>
             </numRef>
           </val>
         </ser>
@@ -1203,171 +1228,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>EC2 Network Usage (MB)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="002060"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr sz="1200" b="1">
-            <a:solidFill>
-              <a:srgbClr val="002060"/>
-            </a:solidFill>
-            <a:latin typeface="Calibri"/>
-          </a:endParaRPr>
-        </a:p>
-      </txPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <v>Network In (MB)</v>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$A$134:$A$141</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$B$134:$B$141</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <v>Network Out (MB)</v>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Dashboard'!$A$134:$A$141</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Dashboard'!$C$134:$C$141</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="800" b="0">
-                <a:solidFill>
-                  <a:srgbClr val="333333"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="800" b="0">
-                <a:solidFill>
-                  <a:srgbClr val="333333"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>S3 Storage Distribution</a:t>
             </a:r>
           </a:p>
@@ -1404,7 +1264,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!B143</f>
+              <f>'Dashboard'!B133</f>
             </strRef>
           </tx>
           <spPr>
@@ -1541,12 +1401,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$144:$A$154</f>
+              <f>'Dashboard'!$A$134:$A$144</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$144:$B$154</f>
+              <f>'Dashboard'!$B$134:$B$144</f>
             </numRef>
           </val>
         </ser>
@@ -1562,7 +1422,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -1623,12 +1483,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$157:$A$159</f>
+              <f>'Dashboard'!$A$147:$A$149</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$157:$B$159</f>
+              <f>'Dashboard'!$B$147:$B$149</f>
             </numRef>
           </val>
         </ser>
@@ -1832,9 +1692,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="4320000"/>
@@ -1854,7 +1714,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>41</row>
       <rowOff>0</rowOff>
@@ -1876,9 +1736,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="4320000"/>
@@ -1898,7 +1758,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>61</row>
       <rowOff>0</rowOff>
@@ -1913,28 +1773,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>61</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5760000" cy="4320000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="8" name="Chart 8"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2399,7 +2237,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>October 04, 2026  09:56 PM</t>
+          <t>October 04, 2026  10:56 PM</t>
         </is>
       </c>
     </row>
@@ -2432,13 +2270,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
@@ -2452,16 +2290,463 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
-        <is>
-          <t>No RDS instances available.</t>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>RDS Name</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Down Time</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Instance type</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Minimum Utilization</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Maximum Utilization</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Average Utilization</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Free Memory</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Free Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Bandwidth and Network status</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>RDS Name</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Network Transmit Throughput (Bytes per second)</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Network Receive Throughput (Bytes per second)</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Max Database Connection (Count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:H3"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2475,7 +2760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P159"/>
+  <dimension ref="A1:P149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -2493,9 +2778,9 @@
       </c>
     </row>
     <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="30" t="inlineStr">
-        <is>
-          <t>Amazon Inspector: 20 findings (Critical 2, High 6)   |   Amazon GuardDuty: 8 findings (High 3). See the Inspector and GuardDuty sheets for detail.</t>
+      <c r="A84" s="31" t="inlineStr">
+        <is>
+          <t>Amazon Inspector: 464 findings (Critical 39, High 200)   |   Amazon GuardDuty: 66 findings (High 0). See the Inspector and GuardDuty sheets for detail.</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2803,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>420.5</v>
+        <v>97.65000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -2528,7 +2813,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>435.1</v>
+        <v>103.15</v>
       </c>
     </row>
     <row r="88">
@@ -2538,7 +2823,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>415.8</v>
+        <v>98.95</v>
       </c>
     </row>
     <row r="89">
@@ -2548,7 +2833,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>460.25</v>
+        <v>104.75</v>
       </c>
     </row>
     <row r="90">
@@ -2558,7 +2843,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>450.4</v>
+        <v>98.55</v>
       </c>
     </row>
     <row r="91">
@@ -2568,7 +2853,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>470.15</v>
+        <v>102.25</v>
       </c>
     </row>
     <row r="92">
@@ -2578,7 +2863,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>464.25</v>
+        <v>99.95</v>
       </c>
     </row>
     <row r="94">
@@ -2596,81 +2881,81 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Amazon Elastic Compute Cloud - Compute</t>
+          <t>Fortinet FortiGate VM Next-Generation Firewall</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1850.2</v>
+        <v>171.36</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Amazon Relational Database Service</t>
+          <t>Elastic Load Balancing</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>720.5</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Amazon Simple Storage Service</t>
+          <t>EC2-Other</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>310.25</v>
+        <v>86.43000000000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Elastic Load Balancing</t>
+          <t>Savings Plans for Compute Usage</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>120.4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS WAF</t>
+          <t>CloudWatch</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>85.09999999999999</v>
+        <v>77.64</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Amazon CloudWatch</t>
+          <t>Relational Database Service</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>30</v>
+        <v>73.68000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Amazon Inspector</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>18.4</v>
+        <v>28.11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Amazon GuardDuty</t>
+          <t>VPC</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>12.75</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="104">
@@ -2688,81 +2973,81 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>InSync Add-in Server</t>
+          <t>Fortinet-FW</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>4.79</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ISTARI-DB Server</t>
+          <t>FLY91- Staging Website</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.28</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>InSync Website Server</t>
+          <t>FLY91- Production Website</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2.47</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>InSync ClickHouse-Database</t>
+          <t>Fly91-SFTP</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>6.02</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>InSync Nexus Server</t>
+          <t>Fly91-Desk</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>7.63</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>InSync Weave-Server</t>
+          <t>Fly91-Development-Server-Windows</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>6.54</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>InSync-Pipelines Server</t>
+          <t>Fly91-Development-Server-Ubuntu</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.46</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ISTARI-App-Server-ASG</t>
+          <t>FLY91 - Data Science Production</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1.51</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="114">
@@ -2773,78 +3058,78 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Avg Memory (%)</t>
+          <t>Disk Usage (%)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>InSync Add-in Server</t>
+          <t>FLY91- Staging Website</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>56.9</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ISTARI-DB Server</t>
+          <t>FLY91- Production Website</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>12.2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>InSync Website Server</t>
+          <t>Fly91-SFTP</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>31.9</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>InSync ClickHouse-Database</t>
+          <t>Fly91-Desk</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>33.2</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>InSync Nexus Server</t>
+          <t>Fly91-Development-Server-Windows</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>InSync Weave-Server</t>
+          <t>Fly91-Development-Server-Ubuntu</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>20.5</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>InSync-Pipelines Server</t>
+          <t>FLY91 - Data Science Production</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>48.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="123">
@@ -2855,221 +3140,229 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Disk Usage (%)</t>
+          <t>Network In (MB)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Network Out (MB)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>InSync Add-in Server</t>
+          <t>Fortinet-FW</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>48.9</v>
+        <v>1228.8</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1290.24</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ISTARI-DB Server</t>
+          <t>FLY91- Staging Website</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>23</v>
+        <v>1341.44</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1597.44</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>InSync Website Server</t>
+          <t>FLY91- Production Website</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>12</v>
+        <v>634.38</v>
+      </c>
+      <c r="C126" t="n">
+        <v>855.01</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>InSync ClickHouse-Database</t>
+          <t>Fly91-SFTP</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>39.5</v>
+        <v>88.54000000000001</v>
+      </c>
+      <c r="C127" t="n">
+        <v>14.32</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>InSync Nexus Server</t>
+          <t>Fly91-Desk</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>71</v>
+        <v>88.29000000000001</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>InSync Weave-Server</t>
+          <t>Fly91-Development-Server-Windows</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>49.5</v>
+        <v>63.74</v>
+      </c>
+      <c r="C129" t="n">
+        <v>10.83</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>InSync-Pipelines Server</t>
+          <t>Fly91-Development-Server-Ubuntu</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>61.5</v>
+        <v>186.64</v>
+      </c>
+      <c r="C130" t="n">
+        <v>141.11</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ISTARI-App-Server-ASG</t>
+          <t>FLY91 - Data Science Production</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>13.5</v>
+        <v>109.23</v>
+      </c>
+      <c r="C131" t="n">
+        <v>48.32</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Instance</t>
+          <t>Bucket</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Network In (MB)</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Network Out (MB)</t>
+          <t>Size (GB)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>InSync Add-in Server</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>390</v>
-      </c>
-      <c r="C134" t="n">
-        <v>810</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ISTARI-DB Server</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>251</v>
-      </c>
-      <c r="C135" t="n">
-        <v>672</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>InSync Website Server</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>168</v>
-      </c>
-      <c r="C136" t="n">
-        <v>247</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>InSync ClickHouse-Database</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>694</v>
-      </c>
-      <c r="C137" t="n">
-        <v>1228.8</v>
+        <v>183</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>InSync Nexus Server</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1228.8</v>
-      </c>
-      <c r="C138" t="n">
-        <v>421</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>InSync Weave-Server</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>261</v>
-      </c>
-      <c r="C139" t="n">
-        <v>12</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>InSync-Pipelines Server</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2048</v>
-      </c>
-      <c r="C140" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ISTARI-App-Server-ASG</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>575</v>
-      </c>
-      <c r="C141" t="n">
-        <v>241</v>
+        <v>259.8</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>228.1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Size (GB)</t>
-        </is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="144">
@@ -3079,149 +3372,49 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>0.88</v>
+          <t>ALB Name</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Stage-Fly91-ALB</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>183</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Prod-Fly91-ALB</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3.2</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Fly91-Development-ALB</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>9.699999999999999</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>259.8</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>228.1</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>ALB Name</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>ISTARI-ALB</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>NEXUS-ALB</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>34000</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Weave-ALB</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>1640</v>
+        <v>2340</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3277,7 +3470,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>$3,116.45</t>
+          <t>$705.25</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3482,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>$3,250.00</t>
+          <t>$728.33</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3494,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>-$133.55  (↓ 4.1%)</t>
+          <t>-$23.08  (↓ 3.2%)</t>
         </is>
       </c>
     </row>
@@ -3313,14 +3506,14 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>$445.21</t>
+          <t>$100.75</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>✅  Cost decreased by 4.1% compared to the previous week. Optimisation efforts are yielding results.</t>
+          <t>✅  Cost decreased by 3.2% compared to the previous week. Optimisation efforts are yielding results.</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3568,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -3387,141 +3580,151 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>54.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Avg Memory Utilisation</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>36.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Peak Memory Utilisation</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>57.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+          <t>77.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>📋 Service Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>EC2 Instances</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Load Balancers (ALB)</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>EC2 Instances</t>
+          <t>WAF Web ACLs</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Load Balancers (ALB)</t>
+          <t>S3 Buckets</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>WAF Web ACLs</t>
+          <t>RDS Instances</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>S3 Buckets</t>
+          <t>Security Findings</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>RDS Instances</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Security Findings</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Inspector 20 (Crit/High 8)  |  GuardDuty 8 (High 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+          <t>Inspector 464 (Crit/High 239)  |  GuardDuty 66 (High 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>🚦 Health Status</t>
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Cost Trend</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>🟢 HEALTHY</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Cost within normal range</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Details</t>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>CPU Utilisation</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>🟢 HEALTHY</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>All instances below 70%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Cost Trend</t>
+          <t>Memory Utilisation</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
@@ -3531,14 +3734,14 @@
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>Cost within normal range</t>
+          <t>No data / all nominal</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>CPU Utilisation</t>
+          <t>WAF Security</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
@@ -3548,14 +3751,14 @@
       </c>
       <c r="D35" s="18" t="inlineStr">
         <is>
-          <t>All instances below 70%</t>
+          <t>93,760 requests blocked</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Memory Utilisation</t>
+          <t>RDS Health</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
@@ -3565,58 +3768,24 @@
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>All instances below threshold</t>
+          <t>All databases healthy</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>WAF Security</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>🟢 HEALTHY</t>
+          <t>Security Findings</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>🔴 CRITICAL</t>
         </is>
       </c>
       <c r="D37" s="18" t="inlineStr">
         <is>
-          <t>15 requests blocked</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>RDS Health</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>🟢 HEALTHY</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>No RDS instances in scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>Security Findings</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>🔴 CRITICAL</t>
-        </is>
-      </c>
-      <c r="D39" s="18" t="inlineStr">
-        <is>
-          <t>2 Critical, 9 High finding(s) this week</t>
+          <t>39 Critical, 200 High finding(s) this week</t>
         </is>
       </c>
     </row>
@@ -3624,10 +3793,10 @@
   <mergeCells count="6">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3640,12 +3809,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -3686,7 +3855,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>$3,250.00</t>
+          <t>$728.33</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3867,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>$3,116.45</t>
+          <t>$705.25</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3879,7 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>$-133.55</t>
+          <t>$-23.08</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3891,7 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>-4.11%</t>
+          <t>-3.17%</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3903,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>$445.21</t>
+          <t>$100.75</t>
         </is>
       </c>
     </row>
@@ -3774,17 +3943,17 @@
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Amazon Elastic Compute Cloud - Compute</t>
+          <t>Fortinet FortiGate VM Next-Generation Firewall</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>$1,850.20</t>
+          <t>$171.36</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
     </row>
@@ -3794,17 +3963,17 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>Amazon Relational Database Service</t>
+          <t>Elastic Load Balancing</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>$720.50</t>
+          <t>$106.97</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -3814,17 +3983,17 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Amazon Simple Storage Service</t>
+          <t>EC2-Other</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>$310.25</t>
+          <t>$86.43</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
@@ -3834,17 +4003,17 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>Elastic Load Balancing</t>
+          <t>Savings Plans for Compute Usage</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>$120.40</t>
+          <t>$84.00</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -3854,17 +4023,17 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>AWS WAF</t>
+          <t>CloudWatch</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>$85.10</t>
+          <t>$77.64</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
     </row>
@@ -3874,17 +4043,17 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>Amazon CloudWatch</t>
+          <t>Relational Database Service</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>$30.00</t>
+          <t>$73.68</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -3894,17 +4063,17 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>Amazon Inspector</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>$18.40</t>
+          <t>$28.11</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -3914,188 +4083,447 @@
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>Amazon GuardDuty</t>
+          <t>VPC</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>$12.75</t>
+          <t>$21.93</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+          <t>3.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>EC2-Instances</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>$20.01</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>GuardDuty</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>$12.52</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>WAF</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>$11.70</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Inspector</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>$7.85</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>1.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>$1.21</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>$0.72</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>Route 53</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>$0.35</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Service-Level Cost Changes</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="13" t="inlineStr">
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>Cost ($)</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Change Indicator</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Amazon Elastic Compute Cloud - Compute</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>↓ -2.5%</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>$1,850.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>Amazon Relational Database Service</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>↑ +1.2%</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>$720.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Amazon Simple Storage Service</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>↑ +4.5%</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>$310.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="18" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Fortinet FortiGate VM Next-Generation Firewall</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>→ No change</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>$171.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>Elastic Load Balancing</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>↓ -0.8%</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>$120.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>AWS WAF</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>↑ +12.0%</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>$85.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>Amazon CloudWatch</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>↓ -11.3%</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>$106.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>EC2-Other</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>↑ +0.3%</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>$86.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Savings Plans for Compute Usage</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>→ No change</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>$30.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>Amazon Inspector</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>↑ +3.4%</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>$18.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>Amazon GuardDuty</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>↑ +2.0%</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>$12.75</t>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>$84.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>CloudWatch</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>↓ -1.4%</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>$77.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>Relational Database Service</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>↓ -8.5%</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>$73.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>↑ +0.5%</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>$28.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>VPC</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>↓ -1.9%</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>$21.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>EC2-Instances</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>↓ -3.1%</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>$20.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>GuardDuty</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>↓ -0.9%</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>$12.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>WAF</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>↓ -7.6%</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>$11.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Inspector</t>
+        </is>
+      </c>
+      <c r="C42" s="27" t="inlineStr">
+        <is>
+          <t>→ No change</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>$7.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>↓ -1.6%</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>$1.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>↑ +22.0%</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t>$0.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Route 53</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>↑ +2.9%</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>$0.35</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F31"/>
+  <autoFilter ref="A4:F45"/>
   <mergeCells count="4">
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4111,14 +4539,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -4181,67 +4609,63 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>InSync Add-in Server</t>
+          <t>Fortinet-FW</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>i-07c0fb23505c71dd8</t>
+          <t>i-06a53ce120fca7a28</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>r6a.8xlarge</t>
+          <t>c6i.xlarge</t>
         </is>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>18</v>
+        <v>6.19</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="G5" s="24" t="n">
-        <v>57</v>
+        <v>0.83</v>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>C: Min 48.9% Max 49.0% Avg 49.0% | D: Min 12.3% Max 12.8% Avg 12.4%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>ISTARI-App Server</t>
+          <t>FLY91- Staging Website</t>
         </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>i-0e68af64896637538</t>
+          <t>i-041cbf2e1ea9a05ee</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>m7i.large</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>t3a.xlarge</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>9.19</v>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
@@ -4250,53 +4674,55 @@
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>91.6%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>ISTARI-DB Server</t>
+          <t>FLY91- Production Website</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>i-0bc7cb7733cccd23b</t>
+          <t>i-056b66d8b569a4a26</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>m7i.12xlarge</t>
+          <t>r6a.xlarge</t>
         </is>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.16</v>
+        <v>2.79</v>
       </c>
       <c r="E7" s="24" t="n">
-        <v>1.86</v>
+        <v>77.11</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <v>12.8</v>
+        <v>8.869999999999999</v>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
-          <t>/ Min 23.0% Max 24.0% Avg 23.6%</t>
+          <t>49.0%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>InSync Website Server</t>
+          <t>Fly91-SFTP</t>
         </is>
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>i-0a8f07365bce735f6</t>
+          <t>i-0b108151d07fe2bf8</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
@@ -4305,183 +4731,199 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1.42</v>
+        <v>2.65</v>
       </c>
       <c r="E8" s="25" t="n">
-        <v>54.4</v>
+        <v>49.97</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>33.2</v>
+        <v>3.89</v>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>/ Min 12.0% Max 13.5% Avg 12.8%</t>
+          <t>76.3%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>InSync ClickHouse-Database</t>
+          <t>Fly91-Desk</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>i-029867634022c4d78</t>
+          <t>i-0e24da06be3f86a40</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>c7i.12xlarge</t>
+          <t>t3a.medium</t>
         </is>
       </c>
       <c r="D9" s="24" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="E9" s="24" t="n">
-        <v>22.2</v>
+        <v>28.72</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>35</v>
+        <v>1.8</v>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>/ Min 39.5% Max 41.2% Avg 40.3%</t>
+          <t>21.8%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>InSync Nexus Server</t>
+          <t>FLY91-Website-testing</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>i-09a1b5ff52381b04b</t>
+          <t>i-0d0653d04b9306f42</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>m6i.8xlarge</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="E10" s="25" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>52.5</v>
+          <t>r6a.large</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H10" s="25" t="inlineStr">
         <is>
-          <t>/ Min 71.0% Max 74.5% Avg 72.8%</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>InSync Weave-Server</t>
+          <t>Fly91-Development-Server-Windows</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>i-05966c44f5be655cc</t>
+          <t>i-00a0097da058e39a1</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>c7i.12xlarge</t>
+          <t>t3a.xlarge</t>
         </is>
       </c>
       <c r="D11" s="24" t="n">
-        <v>6.12</v>
+        <v>9.93</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>10.7</v>
+        <v>58.83</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>21.5</v>
+        <v>14.3</v>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>/ Min 49.5% Max 52.0% Avg 50.9%</t>
+          <t>C: 51.3%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>InSync-Pipelines Server</t>
+          <t>Fly91-Development-Server-Ubuntu</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>i-08b99bf46815a7d38</t>
+          <t>i-0233bf5f2a51870df</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>m7i.large</t>
+          <t>t3a.xlarge</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>1.04</v>
+        <v>2.49</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>7.13</v>
+        <v>42.45</v>
       </c>
       <c r="F12" s="25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="G12" s="25" t="n">
-        <v>50</v>
+        <v>5.77</v>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>/ Min 61.5% Max 65.0% Avg 63.3%</t>
+          <t>87.7%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>ISTARI-App-Server-ASG</t>
+          <t>FLY91 - Data Science Production</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>i-06559919372821d45</t>
+          <t>i-08b66727cdf8d5896</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>c7i.12xlarge</t>
+          <t>t3a.large</t>
         </is>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>4.28</v>
+        <v>32.93</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>1.51</v>
+        <v>5.15</v>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
@@ -4490,7 +4932,7 @@
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>/ Min 13.5% Max 15.2% Avg 14.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -4537,288 +4979,288 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>InSync Add-in Server</t>
+          <t>Fortinet-FW</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>i-07c0fb23505c71dd8</t>
+          <t>i-06a53ce120fca7a28</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>408.94 MB</t>
+          <t>1.29 GB</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>849.35 MB</t>
+          <t>1.35 GB</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>263.00K</t>
+          <t>952.35K</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>380.00K</t>
+          <t>955.08K</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>ISTARI-App Server</t>
+          <t>FLY91- Staging Website</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>i-0e68af64896637538</t>
+          <t>i-041cbf2e1ea9a05ee</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.41 GB</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.68 GB</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.03M</t>
         </is>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.10M</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>ISTARI-DB Server</t>
+          <t>FLY91- Production Website</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>i-0bc7cb7733cccd23b</t>
+          <t>i-056b66d8b569a4a26</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>263.19 MB</t>
+          <t>665.20 MB</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>704.64 MB</t>
+          <t>896.54 MB</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>128.00K</t>
+          <t>446.27K</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>292.00K</t>
+          <t>169.12K</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>InSync Website Server</t>
+          <t>Fly91-SFTP</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>i-0a8f07365bce735f6</t>
+          <t>i-0b108151d07fe2bf8</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>176.16 MB</t>
+          <t>92.84 MB</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>259.00 MB</t>
+          <t>15.02 MB</t>
         </is>
       </c>
       <c r="E20" s="25" t="inlineStr">
         <is>
-          <t>24.00K</t>
+          <t>58.77K</t>
         </is>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>102.00K</t>
+          <t>17.50K</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>InSync ClickHouse-Database</t>
+          <t>Fly91-Desk</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>i-029867634022c4d78</t>
+          <t>i-0e24da06be3f86a40</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>727.71 MB</t>
+          <t>92.58 MB</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>1.29 GB</t>
+          <t>435.06 KB</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>461.00K</t>
+          <t>58.60K</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>509.00K</t>
+          <t>3.64K</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>InSync Nexus Server</t>
+          <t>FLY91-Website-testing</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>i-09a1b5ff52381b04b</t>
+          <t>i-0d0653d04b9306f42</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>1.29 GB</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
-          <t>441.45 MB</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E22" s="25" t="inlineStr">
         <is>
-          <t>1.40M</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>108.00K</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>InSync Weave-Server</t>
+          <t>Fly91-Development-Server-Windows</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>i-05966c44f5be655cc</t>
+          <t>i-00a0097da058e39a1</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>273.68 MB</t>
+          <t>66.84 MB</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>12.58 MB</t>
+          <t>11.36 MB</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>273.00K</t>
+          <t>42.44K</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>22.00K</t>
+          <t>16.41K</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>InSync-Pipelines Server</t>
+          <t>Fly91-Development-Server-Ubuntu</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>i-08b99bf46815a7d38</t>
+          <t>i-0233bf5f2a51870df</t>
         </is>
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>2.15 GB</t>
+          <t>195.71 MB</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>105.91 MB</t>
+          <t>147.96 MB</t>
         </is>
       </c>
       <c r="E24" s="25" t="inlineStr">
         <is>
-          <t>98.00K</t>
+          <t>136.22K</t>
         </is>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>47.20K</t>
+          <t>97.71K</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>ISTARI-App-Server-ASG</t>
+          <t>FLY91 - Data Science Production</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>i-06559919372821d45</t>
+          <t>i-08b66727cdf8d5896</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>602.93 MB</t>
+          <t>114.54 MB</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>252.71 MB</t>
+          <t>50.67 MB</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>424.00K</t>
+          <t>75.59K</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>21.60K</t>
+          <t>33.80K</t>
         </is>
       </c>
     </row>
@@ -4961,120 +5403,120 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>ISTARI-ALB</t>
+          <t>Stage-Fly91-ALB</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>18.90K</t>
+          <t>1.12K</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>28.00K</t>
+          <t>2.24K</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>13.10K</t>
+          <t>1.60K</t>
         </is>
       </c>
       <c r="E5" s="24" t="n">
-        <v>0.02</v>
+        <v>2.41</v>
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>1.78 MB</t>
+          <t>2.59 GB</t>
         </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>1.740 s</t>
+          <t>1.109 s</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>NEXUS-ALB</t>
+          <t>Prod-Fly91-ALB</t>
         </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>34.00K</t>
+          <t>25.00K</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>45.50K</t>
+          <t>4.36K</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>18.40K</t>
+          <t>8.56K</t>
         </is>
       </c>
       <c r="E6" s="25" t="n">
-        <v>0.02</v>
+        <v>3.08</v>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>2.20 MB</t>
+          <t>3.31 GB</t>
         </is>
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>360.0 ms</t>
+          <t>322.8 ms</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>Weave-ALB</t>
+          <t>Fly91-Development-ALB</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>1.64K</t>
+          <t>2.34K</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>4.60K</t>
+          <t>843</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>6.13K</t>
+          <t>3.37K</t>
         </is>
       </c>
       <c r="E7" s="24" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>2.09K</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>312.48 MB</t>
+          <t>18.56 MB</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
-          <t>830.0 ms</t>
+          <t>274.7 ms</t>
         </is>
       </c>
     </row>
@@ -5095,10 +5537,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -5144,50 +5586,72 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>Istari-App-NewDeployment</t>
+          <t>Prod-WAF-Fly-91</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>7.66K</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>9.15M</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>88.72K</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>7.62K</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+          <t>9.06M</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Stag-WAF-Fly-91</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>246.45K</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>5.04K</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>241.41K</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t>7.66K</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>7.62K</t>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>9.40M</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>93.76K</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>9.30M</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D7"/>
+  <autoFilter ref="A4:D8"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
@@ -5257,7 +5721,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -5267,17 +5731,17 @@
         </is>
       </c>
       <c r="B8" s="19" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>7</v>
+      <c r="B9" s="28" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -5287,7 +5751,7 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -5297,17 +5761,17 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n">
-        <v>20</v>
+      <c r="B12" s="27" t="n">
+        <v>464</v>
       </c>
     </row>
     <row r="13"/>
@@ -5657,7 +6121,7 @@
           <t>CVE-2023-29491 - ncurses local privilege escalation</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5694,7 +6158,7 @@
           <t>CVE-2022-37434 - zlib heap buffer over-read</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5731,7 +6195,7 @@
           <t>CVE-2023-0286 - OpenSSL X.400 type confusion</t>
         </is>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5768,7 +6232,7 @@
           <t>CVE-2023-27536 - curl GSSAPI credential reuse</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5805,7 +6269,7 @@
           <t>CVE-2022-40674 - expat use-after-free</t>
         </is>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5842,7 +6306,7 @@
           <t>CVE-2021-3711 - OpenSSL SM2 decryption buffer overflow</t>
         </is>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5879,7 +6343,7 @@
           <t>CVE-2022-3602 - OpenSSL X.509 punycode buffer overflow</t>
         </is>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6179,17 +6643,17 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>3</v>
+      <c r="B8" s="28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6199,17 +6663,17 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n">
-        <v>8</v>
+      <c r="B10" s="27" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="11"/>
@@ -6407,7 +6871,7 @@
           <t>Unprotected port on EC2 instance i-07c0fb23505c71dd8 is being probed</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6450,7 +6914,7 @@
           <t>API GeneratedFindingAPIName was invoked from a Tor exit node</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6493,7 +6957,7 @@
           <t>EC2 instance i-05966c44f5be655cc is performing outbound port scans</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -6919,17 +7383,17 @@
     </row>
     <row r="19"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>737.39 GB</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>2.11M</t>
         </is>

--- a/demo/Fly91_Weekly_AWS_BAU_Report_14-20_Sep_2026.xlsx
+++ b/demo/Fly91_Weekly_AWS_BAU_Report_14-20_Sep_2026.xlsx
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>October 04, 2026  10:56 PM</t>
+          <t>October 05, 2026  12:16 AM</t>
         </is>
       </c>
     </row>

--- a/demo/Fly91_Weekly_AWS_BAU_Report_14-20_Sep_2026.xlsx
+++ b/demo/Fly91_Weekly_AWS_BAU_Report_14-20_Sep_2026.xlsx
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>October 05, 2026  12:16 AM</t>
+          <t>October 05, 2026  06:56 PM</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,8 @@
       <c r="F6" s="25" t="n">
         <v>9.19</v>
       </c>
-      <c r="G6" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G6" s="25" t="n">
+        <v>50.62</v>
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
@@ -4703,10 +4701,8 @@
       <c r="F7" s="24" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="G7" s="24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G7" s="24" t="n">
+        <v>48.23</v>
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
@@ -4739,10 +4735,8 @@
       <c r="F8" s="25" t="n">
         <v>3.89</v>
       </c>
-      <c r="G8" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G8" s="25" t="n">
+        <v>25.35</v>
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
@@ -4775,10 +4769,8 @@
       <c r="F9" s="24" t="n">
         <v>1.8</v>
       </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G9" s="24" t="n">
+        <v>73.97</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
@@ -4853,10 +4845,8 @@
       <c r="F11" s="24" t="n">
         <v>14.3</v>
       </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G11" s="24" t="n">
+        <v>55.21</v>
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
@@ -4889,10 +4879,8 @@
       <c r="F12" s="25" t="n">
         <v>5.77</v>
       </c>
-      <c r="G12" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G12" s="25" t="n">
+        <v>48.75</v>
       </c>
       <c r="H12" s="25" t="inlineStr">
         <is>
@@ -4925,10 +4913,8 @@
       <c r="F13" s="24" t="n">
         <v>5.15</v>
       </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G13" s="24" t="n">
+        <v>9.220000000000001</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>

--- a/demo/Fly91_Weekly_AWS_BAU_Report_14-20_Sep_2026.xlsx
+++ b/demo/Fly91_Weekly_AWS_BAU_Report_14-20_Sep_2026.xlsx
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>October 05, 2026  06:56 PM</t>
+          <t>October 05, 2026  07:00 PM</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-data-science-production-db</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
@@ -2345,39 +2345,39 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>db.t4g.small</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.61%</t>
         </is>
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.74%</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.5 GB out of 2GB</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15.8GB out of 20 GB</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-db</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -2387,39 +2387,39 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>db.r7g.large</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47.49%</t>
         </is>
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.72%</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.86GB out of 16 GB</t>
         </is>
       </c>
       <c r="H5" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>89.1GB out of 100 GB</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-dev-db</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
@@ -2429,39 +2429,39 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>db.t3.large</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14.41%</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>46.17%</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.86GB out of 8 GB</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21.4GB out of 30 GB</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-development-psql</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -2471,39 +2471,39 @@
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>db.t3.medium</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.44%</t>
         </is>
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>79.77%</t>
         </is>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13.32%</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.90GB out of 4 GB</t>
         </is>
       </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.8GB out of 77 GB</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-prod-psql-db</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
@@ -2513,39 +2513,39 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>db.t3.large</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>43.76%</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.35GB out of 8 GB</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.0GB out of 100 GB</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-uat-psql-db</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
@@ -2555,32 +2555,32 @@
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>db.t3.medium</t>
         </is>
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>99.57%</t>
         </is>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00GB out of 4 GB</t>
         </is>
       </c>
       <c r="H9" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27.1GB out of 50 GB</t>
         </is>
       </c>
     </row>
@@ -2616,132 +2616,132 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-data-science-production-db</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>817.54 KB</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>77.25 KB</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-db</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24.70 MB</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.52 MB</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-dev-db</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15.78 MB</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>142.12 KB</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-development-psql</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15.58 MB</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.50 MB</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>134</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-prod-psql-db</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.79 MB</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.21 MB</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>210</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>fly91-uat-psql-db</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18.92 MB</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>772.02 KB</t>
         </is>
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>193</t>
         </is>
       </c>
     </row>

--- a/demo/Fly91_Weekly_AWS_BAU_Report_14-20_Sep_2026.xlsx
+++ b/demo/Fly91_Weekly_AWS_BAU_Report_14-20_Sep_2026.xlsx
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>October 05, 2026  07:00 PM</t>
+          <t>October 05, 2026  07:22 PM</t>
         </is>
       </c>
     </row>
